--- a/4_analisis/salidas/hipotesis_electoral/tablas_hipotesis_electoral.xlsx
+++ b/4_analisis/salidas/hipotesis_electoral/tablas_hipotesis_electoral.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>337.7</v>
+        <v>337.2</v>
       </c>
     </row>
     <row r="6">
@@ -514,19 +514,19 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>375.6</v>
+        <v>374.9</v>
       </c>
       <c r="D6" t="n">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="E6" t="n">
         <v>0.88</v>
       </c>
       <c r="F6" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>401.9</v>
+        <v>401.1</v>
       </c>
       <c r="D7" t="n">
         <v>6.99</v>
@@ -556,16 +556,16 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>478.5</v>
+        <v>477.7</v>
       </c>
       <c r="D8" t="n">
-        <v>19.05</v>
+        <v>19.07</v>
       </c>
       <c r="E8" t="n">
         <v>9.34</v>
       </c>
       <c r="F8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G8" t="n">
         <v>0.458</v>
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>569.3</v>
+        <v>568.2</v>
       </c>
       <c r="D9" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
       <c r="E9" t="n">
         <v>6.95</v>
       </c>
       <c r="F9" t="n">
-        <v>12.03</v>
+        <v>12.01</v>
       </c>
       <c r="G9" t="n">
-        <v>0.632</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10">
@@ -602,19 +602,19 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>627.4</v>
+        <v>626.7</v>
       </c>
       <c r="D10" t="n">
-        <v>10.21</v>
+        <v>10.29</v>
       </c>
       <c r="E10" t="n">
         <v>1.89</v>
       </c>
       <c r="F10" t="n">
-        <v>8.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.51</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="11">
@@ -623,7 +623,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>618.9</v>
+        <v>618.1</v>
       </c>
       <c r="D11" t="n">
         <v>-1.37</v>
@@ -644,7 +644,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>653.7</v>
+        <v>652.8</v>
       </c>
       <c r="D12" t="n">
         <v>5.62</v>
@@ -653,10 +653,10 @@
         <v>-0.49</v>
       </c>
       <c r="F12" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>718.6</v>
+        <v>717.8</v>
       </c>
       <c r="D13" t="n">
-        <v>9.93</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>7.74</v>
       </c>
       <c r="F13" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="14">
@@ -693,16 +693,16 @@
         <v>730.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="E14" t="n">
         <v>7.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.15</v>
+        <v>-6.04</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.403</v>
+        <v>-0.395</v>
       </c>
     </row>
     <row r="15">
@@ -727,28 +727,53 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>2026</v>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="n">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
         <v>814.7</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>5.22</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>4.25</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>0.97</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>0.065</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>976.2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.218</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Nota. Euros constantes de 2025. Fuente: Tomo 3 (tablas 2.8, 2.9 y 2.16). Elaboración propia, ODESOCAN.</t>
         </is>
@@ -765,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -834,7 +859,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>337.7</v>
+        <v>337.2</v>
       </c>
     </row>
     <row r="6">
@@ -843,19 +868,19 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>375.6</v>
+        <v>374.9</v>
       </c>
       <c r="D6" t="n">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="E6" t="n">
         <v>0.88</v>
       </c>
       <c r="F6" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="7">
@@ -864,7 +889,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>401.9</v>
+        <v>401.1</v>
       </c>
       <c r="D7" t="n">
         <v>6.99</v>
@@ -885,16 +910,16 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>478.5</v>
+        <v>477.7</v>
       </c>
       <c r="D8" t="n">
-        <v>19.05</v>
+        <v>19.07</v>
       </c>
       <c r="E8" t="n">
         <v>9.34</v>
       </c>
       <c r="F8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G8" t="n">
         <v>0.458</v>
@@ -910,19 +935,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>569.3</v>
+        <v>568.2</v>
       </c>
       <c r="D9" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
       <c r="E9" t="n">
         <v>6.95</v>
       </c>
       <c r="F9" t="n">
-        <v>12.03</v>
+        <v>12.01</v>
       </c>
       <c r="G9" t="n">
-        <v>0.632</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10">
@@ -931,19 +956,19 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>627.4</v>
+        <v>626.7</v>
       </c>
       <c r="D10" t="n">
-        <v>10.21</v>
+        <v>10.29</v>
       </c>
       <c r="E10" t="n">
         <v>1.89</v>
       </c>
       <c r="F10" t="n">
-        <v>8.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.51</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="11">
@@ -952,7 +977,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>618.9</v>
+        <v>618.1</v>
       </c>
       <c r="D11" t="n">
         <v>-1.37</v>
@@ -973,19 +998,19 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>628.4</v>
+        <v>627.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="E12" t="n">
         <v>-0.49</v>
       </c>
       <c r="F12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="13">
@@ -998,19 +1023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>677.6</v>
+        <v>676.8</v>
       </c>
       <c r="D13" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="E13" t="n">
         <v>7.74</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="14">
@@ -1022,16 +1047,16 @@
         <v>688.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="E14" t="n">
         <v>7.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.16</v>
+        <v>-6.05</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.381</v>
+        <v>-0.373</v>
       </c>
     </row>
     <row r="15">
@@ -1056,28 +1081,53 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>2026</v>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="n">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
         <v>803.6</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>13.24</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>4.25</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>8.99</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>0.551</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>975</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.303</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Nota. Euros constantes de 2025. Fuente: Tomo 3 (tablas 2.8, 2.9 y 2.16). Elaboración propia, ODESOCAN.</t>
         </is>
@@ -1094,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1385,28 +1435,53 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>2026</v>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="n">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
         <v>816.5</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>5.42</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>4.25</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>1.17</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>0.078</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>978.1</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.218</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Nota. Euros constantes de 2025. Fuente: Tomo 3 (tablas 2.8, 2.9 y 2.16). Elaboración propia, ODESOCAN.</t>
         </is>
@@ -1423,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1714,28 +1789,53 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>2026</v>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="n">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
         <v>773.8</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" t="n">
         <v>5.49</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" t="n">
         <v>4.25</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" t="n">
         <v>1.24</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" t="n">
         <v>0.078</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>931.4</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1.192</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Nota. Euros constantes de 2025. Fuente: Tomo 3 (tablas 2.8, 2.9 y 2.16). Elaboración propia, ODESOCAN.</t>
         </is>
@@ -1773,7 +1873,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Contraste de permutación exacta: años electorales (2019, 2023) frente al resto</t>
+          <t>Contraste de permutación exacta: años electorales (2019, 2023, 2027) frente al resto</t>
         </is>
       </c>
     </row>
@@ -1821,16 +1921,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.111</v>
+        <v>10.637</v>
       </c>
       <c r="D5" t="n">
-        <v>3.68</v>
+        <v>3.696</v>
       </c>
       <c r="E5" t="n">
-        <v>3.431</v>
+        <v>6.942</v>
       </c>
       <c r="F5" t="n">
-        <v>0.273</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="6">
@@ -1845,16 +1945,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.386</v>
+        <v>0.663</v>
       </c>
       <c r="D6" t="n">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>0.197</v>
+        <v>0.473</v>
       </c>
       <c r="F6" t="n">
-        <v>0.255</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="7">
@@ -1869,16 +1969,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14.457</v>
+        <v>16.251</v>
       </c>
       <c r="D7" t="n">
-        <v>7.18</v>
+        <v>7.196</v>
       </c>
       <c r="E7" t="n">
-        <v>7.277</v>
+        <v>9.055</v>
       </c>
       <c r="F7" t="n">
-        <v>0.127</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="8">
@@ -1893,16 +1993,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.061</v>
+        <v>10.437</v>
       </c>
       <c r="D8" t="n">
-        <v>3.787</v>
+        <v>3.803</v>
       </c>
       <c r="E8" t="n">
-        <v>2.274</v>
+        <v>6.634</v>
       </c>
       <c r="F8" t="n">
-        <v>0.327</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="9">
@@ -1917,16 +2017,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.319</v>
+        <v>0.647</v>
       </c>
       <c r="D9" t="n">
-        <v>0.193</v>
+        <v>0.194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.125</v>
+        <v>0.453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.345</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1941,16 +2041,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13.406</v>
+        <v>16.051</v>
       </c>
       <c r="D10" t="n">
-        <v>7.287</v>
+        <v>7.303</v>
       </c>
       <c r="E10" t="n">
-        <v>6.119</v>
+        <v>8.747999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.164</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="11">
@@ -1965,16 +2065,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.135</v>
+        <v>10.639</v>
       </c>
       <c r="D11" t="n">
         <v>3.681</v>
       </c>
       <c r="E11" t="n">
-        <v>3.454</v>
+        <v>6.958</v>
       </c>
       <c r="F11" t="n">
-        <v>0.255</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="12">
@@ -1989,16 +2089,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.389</v>
+        <v>0.665</v>
       </c>
       <c r="D12" t="n">
         <v>0.189</v>
       </c>
       <c r="E12" t="n">
-        <v>0.199</v>
+        <v>0.476</v>
       </c>
       <c r="F12" t="n">
-        <v>0.273</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="13">
@@ -2013,16 +2113,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14.481</v>
+        <v>16.253</v>
       </c>
       <c r="D13" t="n">
         <v>7.182</v>
       </c>
       <c r="E13" t="n">
-        <v>7.299</v>
+        <v>9.071</v>
       </c>
       <c r="F13" t="n">
-        <v>0.109</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="14">
@@ -2037,16 +2137,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.671</v>
+        <v>11.187</v>
       </c>
       <c r="D14" t="n">
         <v>3.838</v>
       </c>
       <c r="E14" t="n">
-        <v>3.834</v>
+        <v>7.349</v>
       </c>
       <c r="F14" t="n">
-        <v>0.236</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="15">
@@ -2061,16 +2161,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.393</v>
+        <v>0.659</v>
       </c>
       <c r="D15" t="n">
         <v>0.184</v>
       </c>
       <c r="E15" t="n">
-        <v>0.209</v>
+        <v>0.475</v>
       </c>
       <c r="F15" t="n">
-        <v>0.255</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="16">
@@ -2085,16 +2185,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.017</v>
+        <v>16.8</v>
       </c>
       <c r="D16" t="n">
         <v>7.338</v>
       </c>
       <c r="E16" t="n">
-        <v>7.679</v>
+        <v>9.462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.091</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="17">
@@ -2109,16 +2209,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.164</v>
+        <v>18.504</v>
       </c>
       <c r="D17" t="n">
         <v>7.253</v>
       </c>
       <c r="E17" t="n">
-        <v>2.911</v>
+        <v>11.251</v>
       </c>
       <c r="F17" t="n">
-        <v>0.345</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="18">
@@ -2133,16 +2233,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.217</v>
+        <v>0.542</v>
       </c>
       <c r="D18" t="n">
         <v>0.155</v>
       </c>
       <c r="E18" t="n">
-        <v>0.062</v>
+        <v>0.387</v>
       </c>
       <c r="F18" t="n">
-        <v>0.345</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2157,16 +2257,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.51</v>
+        <v>24.117</v>
       </c>
       <c r="D19" t="n">
         <v>10.753</v>
       </c>
       <c r="E19" t="n">
-        <v>6.757</v>
+        <v>13.364</v>
       </c>
       <c r="F19" t="n">
-        <v>0.273</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2181,16 +2281,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.779</v>
+        <v>3.496</v>
       </c>
       <c r="D20" t="n">
         <v>-0.982</v>
       </c>
       <c r="E20" t="n">
-        <v>8.76</v>
+        <v>4.477</v>
       </c>
       <c r="F20" t="n">
-        <v>0.164</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="21">
@@ -2205,16 +2305,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="D21" t="n">
         <v>-0.004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.031</v>
+        <v>0.013</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="22">
@@ -2229,16 +2329,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.124</v>
+        <v>9.109</v>
       </c>
       <c r="D22" t="n">
         <v>2.519</v>
       </c>
       <c r="E22" t="n">
-        <v>12.606</v>
+        <v>6.591</v>
       </c>
       <c r="F22" t="n">
-        <v>0.164</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="23">
@@ -2253,16 +2353,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.045</v>
+        <v>-0.282</v>
       </c>
       <c r="D23" t="n">
         <v>10.232</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.186999999999999</v>
+        <v>-10.515</v>
       </c>
       <c r="F23" t="n">
-        <v>0.727</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="24">
@@ -2277,16 +2377,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="D24" t="n">
         <v>0.054</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.044</v>
+        <v>-0.058</v>
       </c>
       <c r="F24" t="n">
-        <v>0.709</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="25">
@@ -2301,16 +2401,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.391</v>
+        <v>5.331</v>
       </c>
       <c r="D25" t="n">
         <v>13.733</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.342</v>
+        <v>-8.401</v>
       </c>
       <c r="F25" t="n">
-        <v>0.655</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="26">
@@ -2325,16 +2425,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11.908</v>
+        <v>12.01</v>
       </c>
       <c r="D26" t="n">
         <v>-3.365</v>
       </c>
       <c r="E26" t="n">
-        <v>15.272</v>
+        <v>15.375</v>
       </c>
       <c r="F26" t="n">
-        <v>0.036</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="27">
@@ -2349,16 +2449,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.117</v>
+        <v>0.114</v>
       </c>
       <c r="D27" t="n">
         <v>-0.038</v>
       </c>
       <c r="E27" t="n">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="F27" t="n">
-        <v>0.036</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="28">
@@ -2373,16 +2473,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19.254</v>
+        <v>17.624</v>
       </c>
       <c r="D28" t="n">
         <v>0.136</v>
       </c>
       <c r="E28" t="n">
-        <v>19.118</v>
+        <v>17.488</v>
       </c>
       <c r="F28" t="n">
-        <v>0.036</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="29">
@@ -2397,16 +2497,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.768</v>
+        <v>-0.61</v>
       </c>
       <c r="D29" t="n">
         <v>4.745</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.977</v>
+        <v>-5.355</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="30">
@@ -2421,16 +2521,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.022</v>
+        <v>-0.001</v>
       </c>
       <c r="D30" t="n">
         <v>0.018</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004</v>
+        <v>-0.019</v>
       </c>
       <c r="F30" t="n">
-        <v>0.545</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="31">
@@ -2445,22 +2545,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>10.114</v>
+        <v>5.004</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>8.244999999999999</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.869</v>
+        <v>-3.241</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.436</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Nota. p unilateral = proporción de las 55 parejas de años con media ≥ la observada.</t>
+          <t>Nota. p unilateral = proporción de las 220 combinaciones de 3 años con media ≥ la observada.</t>
         </is>
       </c>
     </row>
